--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -23,13 +23,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFVitalsSite</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsSite</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet VF_VitalsSite</t>
+    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsSite.xlsx
+++ b/docs/ValueSet-VSVFVitalsSite.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
+    <t>Navigate to the [ConceptMap VF_VitalsSite](ConceptMap-CMVFVitalsSite.html).</t>
   </si>
   <si>
     <t>Purpose</t>
